--- a/trace_compare_final_prefix_code_project/corrected_added_highlight_prefix_logic_output_comparison_output.xlsx
+++ b/trace_compare_final_prefix_code_project/corrected_added_highlight_prefix_logic_output_comparison_output.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison_Output" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1_old" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparison_Output'!$A$1:$O$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparison_Output'!$A$1:$O$52</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +73,22 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <strike val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <strike val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <strike val="1"/>
       <color rgb="FF000000"/>
       <sz val="11"/>
@@ -118,7 +134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -210,6 +226,19 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -234,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -266,25 +295,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -296,9 +328,18 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -666,10 +707,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.54296875" customWidth="1" min="1" max="1"/>
+    <col width="30.5703125" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="33" customHeight="1">
@@ -750,98 +791,98 @@
       </c>
     </row>
     <row r="2" ht="57.75" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000100</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>Project-OBJ-02</t>
         </is>
       </c>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="16" t="n"/>
-      <c r="I2" s="16" t="n"/>
-      <c r="J2" s="17" t="inlineStr">
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="17" t="n"/>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="18" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
         </is>
       </c>
-      <c r="K2" s="17" t="inlineStr">
+      <c r="K2" s="18" t="inlineStr">
         <is>
           <t>Dust/Particulate Control</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
+      <c r="L2" s="18" t="inlineStr">
         <is>
           <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
         </is>
       </c>
-      <c r="M2" s="17" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N2" s="17" t="inlineStr">
+      <c r="M2" s="18" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N2" s="18" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O2" s="17" t="inlineStr">
+      <c r="O2" s="18" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="3" ht="70.5" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000100</t>
         </is>
       </c>
-      <c r="B3" s="19" t="n"/>
-      <c r="C3" s="19" t="n"/>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Project-OBJ-02</t>
         </is>
       </c>
-      <c r="E3" s="19" t="n"/>
-      <c r="F3" s="19" t="n"/>
-      <c r="G3" s="19" t="n"/>
-      <c r="H3" s="19" t="n"/>
-      <c r="I3" s="19" t="n"/>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="20" t="n"/>
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Project-SRS-0009</t>
         </is>
       </c>
-      <c r="K3" s="17" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t>Compressed Air Quality</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="18" t="inlineStr">
         <is>
           <t>The facility must supply compressed air to production equipment at the specified pressure, flow, and cleanliness class at each point of use.</t>
         </is>
       </c>
-      <c r="M3" s="17" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="M3" s="18" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N3" s="18" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O3" s="17" t="inlineStr">
+      <c r="O3" s="18" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -853,201 +894,201 @@
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="n"/>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="12" t="n"/>
       <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Safe, Compliant and Sustainable Operations</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>Project-BRS-0001</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>Safe, Efficient &amp; Compliant Operations</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>The widget factory shall enable safe, efficient, and legally compliant manufacturing operations across all production, logistics, and support activities to protect personnel, assets, and regulatory approvals.</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>Project-SRS-0013</t>
         </is>
       </c>
-      <c r="K4" s="17" t="inlineStr">
+      <c r="K4" s="18" t="inlineStr">
         <is>
           <t>Fire Detection Coverage</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="18" t="inlineStr">
         <is>
           <t>The facility must provide fire and smoke detection coverage for all occupied and operational spaces.</t>
         </is>
       </c>
-      <c r="M4" s="17" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="18" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N4" s="18" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O4" s="17" t="inlineStr">
+      <c r="O4" s="18" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="5" ht="57.75" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>Project-BRS-0001</t>
         </is>
       </c>
-      <c r="H5" s="20" t="n"/>
-      <c r="I5" s="20" t="n"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="21" t="n"/>
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>Project-SRS-0014</t>
         </is>
       </c>
-      <c r="K5" s="17" t="inlineStr">
+      <c r="K5" s="18" t="inlineStr">
         <is>
           <t>Fire Suppression</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="18" t="inlineStr">
         <is>
           <t>The facility must provide fire suppression systems appropriate to the fire hazard classification of each area.</t>
         </is>
       </c>
-      <c r="M5" s="17" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="18" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O5" s="17" t="inlineStr">
+      <c r="O5" s="18" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="6" ht="70.5" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>Project-BRS-0001</t>
         </is>
       </c>
-      <c r="H6" s="19" t="n"/>
-      <c r="I6" s="19" t="n"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>Project-SRS-0001</t>
         </is>
       </c>
-      <c r="K6" s="17" t="inlineStr">
+      <c r="K6" s="18" t="inlineStr">
         <is>
           <t>Site Access &amp; Logistics</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="18" t="inlineStr">
         <is>
           <t>The facility must provide segregated heavy-vehicle and light-vehicle access routes from the site boundary to designated loading and parking areas.</t>
         </is>
       </c>
-      <c r="M6" s="17" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="O6" s="18" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="7" ht="57.75" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
       <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>Workforce Productivity &amp; Support</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
         </is>
@@ -1084,27 +1125,27 @@
       </c>
     </row>
     <row r="8" ht="57.75" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
         </is>
       </c>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="13" t="n"/>
       <c r="J8" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
@@ -1137,27 +1178,27 @@
       </c>
     </row>
     <row r="9" ht="57.75" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
         </is>
       </c>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="13" t="n"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
@@ -1190,27 +1231,27 @@
       </c>
     </row>
     <row r="10" ht="70.5" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
         </is>
       </c>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="n"/>
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="13" t="n"/>
       <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0001</t>
@@ -1243,27 +1284,27 @@
       </c>
     </row>
     <row r="11" ht="57.75" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
         </is>
       </c>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
@@ -1296,31 +1337,31 @@
       </c>
     </row>
     <row r="12" ht="57.75" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Project-BRS-0004</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>Environmental &amp; Community Stewardship</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
         </is>
@@ -1357,27 +1398,27 @@
       </c>
     </row>
     <row r="13" ht="57.75" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>Project-BRS-0004</t>
         </is>
       </c>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0016</t>
@@ -1410,27 +1451,27 @@
       </c>
     </row>
     <row r="14" ht="57.75" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Project-BRS-0004</t>
         </is>
       </c>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
       <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -1463,76 +1504,76 @@
       </c>
     </row>
     <row r="15" ht="57.75" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J15" s="18" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr">
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>Floor Load Rating</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="18" t="inlineStr">
         <is>
           <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="M15" s="18" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N15" s="18" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O15" s="17" t="inlineStr">
+      <c r="O15" s="18" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="16" ht="70.5" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
       <c r="D16" s="10" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
       <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Project-BRS-0002</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>Reliable Manufacturing Capability</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
         </is>
@@ -1569,23 +1610,23 @@
       </c>
     </row>
     <row r="17" ht="57.75" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>Project-BRS-0002</t>
         </is>
       </c>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="n"/>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="13" t="n"/>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
@@ -1618,23 +1659,23 @@
       </c>
     </row>
     <row r="18" ht="57.75" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>Project-BRS-0002</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="11" t="n"/>
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="13" t="n"/>
       <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
@@ -1667,23 +1708,23 @@
       </c>
     </row>
     <row r="19" ht="70.5" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>Project-BRS-0002</t>
         </is>
       </c>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0002</t>
@@ -1716,23 +1757,23 @@
       </c>
     </row>
     <row r="20" ht="57.75" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>Project-BRS-0002</t>
         </is>
       </c>
-      <c r="H20" s="11" t="n"/>
-      <c r="I20" s="11" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="13" t="n"/>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -1765,23 +1806,23 @@
       </c>
     </row>
     <row r="21" ht="70.5" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>Project-BRS-0002</t>
         </is>
       </c>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="13" t="n"/>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0009</t>
@@ -1814,23 +1855,23 @@
       </c>
     </row>
     <row r="22" ht="57.75" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Project-BRS-0002</t>
         </is>
       </c>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
       <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
@@ -1863,19 +1904,19 @@
       </c>
     </row>
     <row r="23" ht="57.75" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
       <c r="G23" s="10" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0005</t>
@@ -1908,19 +1949,19 @@
       </c>
     </row>
     <row r="24" ht="57.75" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="11" t="n"/>
       <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -1953,37 +1994,37 @@
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>Safe, Compliant and Sustainable Operations</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="23" t="n"/>
-      <c r="I25" s="23" t="n"/>
-      <c r="J25" s="24" t="n"/>
-      <c r="K25" s="24" t="n"/>
-      <c r="L25" s="24" t="n"/>
-      <c r="M25" s="24" t="n"/>
-      <c r="N25" s="24" t="n"/>
-      <c r="O25" s="24" t="n"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="24" t="n"/>
+      <c r="I25" s="24" t="n"/>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="25" t="n"/>
+      <c r="L25" s="25" t="n"/>
+      <c r="M25" s="25" t="n"/>
+      <c r="N25" s="25" t="n"/>
+      <c r="O25" s="25" t="n"/>
     </row>
     <row r="26" ht="57.75" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -1999,101 +2040,101 @@
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
-      <c r="J26" s="17" t="inlineStr">
+      <c r="J26" s="18" t="inlineStr">
         <is>
           <t>Project-SRS-0004</t>
         </is>
       </c>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="K26" s="18" t="inlineStr">
         <is>
           <t>Floor Flatness</t>
         </is>
       </c>
-      <c r="L26" s="17" t="inlineStr">
+      <c r="L26" s="18" t="inlineStr">
         <is>
           <t>The production floor must achieve the specified flatness and levelness tolerances required by precision manufacturing equipment.</t>
         </is>
       </c>
-      <c r="M26" s="17" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N26" s="17" t="inlineStr">
+      <c r="M26" s="18" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N26" s="18" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O26" s="17" t="inlineStr">
+      <c r="O26" s="18" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="25" t="n"/>
-      <c r="E27" s="25" t="n"/>
-      <c r="F27" s="25" t="n"/>
-      <c r="G27" s="25" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Project-OBJ-01</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="n"/>
+      <c r="F27" s="26" t="n"/>
+      <c r="G27" s="25" t="n"/>
       <c r="H27" s="25" t="n"/>
       <c r="I27" s="25" t="n"/>
-      <c r="J27" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0009</t>
-        </is>
-      </c>
-      <c r="K27" s="24" t="inlineStr">
-        <is>
-          <t>Compressed Air Quality</t>
-        </is>
-      </c>
-      <c r="L27" s="24" t="inlineStr">
-        <is>
-          <t>The facility must supply compressed air to production equipment at the specified pressure, flow, and cleanliness class at each point of use.</t>
-        </is>
-      </c>
-      <c r="M27" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N27" s="24" t="inlineStr">
+      <c r="J27" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0003</t>
+        </is>
+      </c>
+      <c r="K27" s="25" t="inlineStr">
+        <is>
+          <t>Floor Load Rating</t>
+        </is>
+      </c>
+      <c r="L27" s="25" t="inlineStr">
+        <is>
+          <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
+        </is>
+      </c>
+      <c r="M27" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N27" s="25" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O27" s="24" t="inlineStr">
+      <c r="O27" s="25" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E28" s="25" t="n"/>
-      <c r="F28" s="25" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="27" t="n"/>
       <c r="G28" s="26" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
@@ -2101,893 +2142,893 @@
       </c>
       <c r="H28" s="26" t="n"/>
       <c r="I28" s="26" t="n"/>
-      <c r="J28" s="24" t="inlineStr">
+      <c r="J28" s="25" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
         </is>
       </c>
-      <c r="K28" s="24" t="inlineStr">
+      <c r="K28" s="25" t="inlineStr">
         <is>
           <t>Temperature Control</t>
         </is>
       </c>
-      <c r="L28" s="24" t="inlineStr">
+      <c r="L28" s="25" t="inlineStr">
         <is>
           <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
         </is>
       </c>
-      <c r="M28" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N28" s="24" t="inlineStr">
+      <c r="M28" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N28" s="25" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O28" s="24" t="inlineStr">
+      <c r="O28" s="25" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="26" t="n"/>
-      <c r="G29" s="26" t="n"/>
-      <c r="H29" s="26" t="n"/>
-      <c r="I29" s="26" t="n"/>
-      <c r="J29" s="24" t="inlineStr">
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>Project-OBJ-01</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>Project-BRS-0008</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>Workforce Productivity &amp; Support</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0018</t>
+        </is>
+      </c>
+      <c r="K29" s="25" t="inlineStr">
+        <is>
+          <t>Physical Security Zones</t>
+        </is>
+      </c>
+      <c r="L29" s="25" t="inlineStr">
+        <is>
+          <t>The facility must implement access control to restrict entry to production and warehouse areas to authorised personnel only.</t>
+        </is>
+      </c>
+      <c r="M29" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N29" s="25" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O29" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18.75" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t>Project-OBJ-01</t>
+        </is>
+      </c>
+      <c r="E30" s="27" t="n"/>
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="27" t="inlineStr">
+        <is>
+          <t>Project-BRS-0004</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="n"/>
+      <c r="I30" s="27" t="n"/>
+      <c r="J30" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0016</t>
+        </is>
+      </c>
+      <c r="K30" s="25" t="inlineStr">
+        <is>
+          <t>Wastewater Management</t>
+        </is>
+      </c>
+      <c r="L30" s="25" t="inlineStr">
+        <is>
+          <t>The facility must treat and/or contain process wastewater to meet the discharge acceptance criteria at the defined discharge point.</t>
+        </is>
+      </c>
+      <c r="M30" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N30" s="25" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O30" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18.75" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="27" t="n"/>
+      <c r="E31" s="27" t="n"/>
+      <c r="F31" s="27" t="n"/>
+      <c r="G31" s="23" t="n"/>
+      <c r="H31" s="23" t="n"/>
+      <c r="I31" s="23" t="n"/>
+      <c r="J31" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0005</t>
+        </is>
+      </c>
+      <c r="K31" s="25" t="inlineStr">
+        <is>
+          <t>Building Envelope Tightness</t>
+        </is>
+      </c>
+      <c r="L31" s="25" t="inlineStr">
+        <is>
+          <t>The building envelope must achieve air leakage performance not exceeding the nominated threshold.</t>
+        </is>
+      </c>
+      <c r="M31" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N31" s="25" t="inlineStr">
+        <is>
+          <t>Technical Requirements</t>
+        </is>
+      </c>
+      <c r="O31" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18.75" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>Project-OBJ-01</t>
+        </is>
+      </c>
+      <c r="E32" s="27" t="n"/>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="27" t="inlineStr">
+        <is>
+          <t>Project-BRS-0008</t>
+        </is>
+      </c>
+      <c r="H32" s="27" t="n"/>
+      <c r="I32" s="27" t="n"/>
+      <c r="J32" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0008</t>
+        </is>
+      </c>
+      <c r="K32" s="25" t="inlineStr">
+        <is>
+          <t>Dust/Particulate Control</t>
+        </is>
+      </c>
+      <c r="L32" s="25" t="inlineStr">
+        <is>
+          <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
+        </is>
+      </c>
+      <c r="M32" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N32" s="25" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O32" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18.75" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="27" t="n"/>
+      <c r="E33" s="27" t="n"/>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>Project-BRS-0002</t>
+        </is>
+      </c>
+      <c r="H33" s="26" t="n"/>
+      <c r="I33" s="26" t="n"/>
+      <c r="J33" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0006</t>
+        </is>
+      </c>
+      <c r="K33" s="25" t="inlineStr">
+        <is>
+          <t>Temperature Control</t>
+        </is>
+      </c>
+      <c r="L33" s="25" t="inlineStr">
+        <is>
+          <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
+        </is>
+      </c>
+      <c r="M33" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N33" s="25" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O33" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18.75" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t>Project-OBJ-01</t>
+        </is>
+      </c>
+      <c r="E34" s="27" t="n"/>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="27" t="inlineStr">
+        <is>
+          <t>Project-BRS-0008</t>
+        </is>
+      </c>
+      <c r="H34" s="27" t="n"/>
+      <c r="I34" s="27" t="n"/>
+      <c r="J34" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0007</t>
+        </is>
+      </c>
+      <c r="K34" s="25" t="inlineStr">
+        <is>
+          <t>Humidity Control</t>
+        </is>
+      </c>
+      <c r="L34" s="25" t="inlineStr">
+        <is>
+          <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
+        </is>
+      </c>
+      <c r="M34" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N34" s="25" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O34" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18.75" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="27" t="n"/>
+      <c r="E35" s="27" t="n"/>
+      <c r="F35" s="27" t="n"/>
+      <c r="G35" s="27" t="inlineStr">
+        <is>
+          <t>Project-BRS-0002</t>
+        </is>
+      </c>
+      <c r="H35" s="27" t="n"/>
+      <c r="I35" s="27" t="n"/>
+      <c r="J35" s="25" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
         </is>
       </c>
-      <c r="K29" s="24" t="inlineStr">
+      <c r="K35" s="25" t="inlineStr">
         <is>
           <t>Floor Load Rating</t>
         </is>
       </c>
-      <c r="L29" s="24" t="inlineStr">
+      <c r="L35" s="25" t="inlineStr">
         <is>
           <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
         </is>
       </c>
-      <c r="M29" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N29" s="24" t="inlineStr">
+      <c r="M35" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N35" s="25" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O29" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="O35" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18.75" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="27" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="26" t="n"/>
-      <c r="G30" s="24" t="n"/>
-      <c r="H30" s="24" t="n"/>
-      <c r="I30" s="24" t="n"/>
-      <c r="J30" s="24" t="inlineStr">
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="26" t="inlineStr">
+        <is>
+          <t>Project-BRS-0004</t>
+        </is>
+      </c>
+      <c r="H36" s="26" t="n"/>
+      <c r="I36" s="26" t="n"/>
+      <c r="J36" s="25" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
         </is>
       </c>
-      <c r="K30" s="24" t="inlineStr">
+      <c r="K36" s="25" t="inlineStr">
         <is>
           <t>Floor Load Rating</t>
         </is>
       </c>
-      <c r="L30" s="24" t="inlineStr">
+      <c r="L36" s="25" t="inlineStr">
         <is>
           <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
         </is>
       </c>
-      <c r="M30" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N30" s="24" t="inlineStr">
+      <c r="M36" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N36" s="25" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O30" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="O36" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18.75" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="25" t="n"/>
-      <c r="E31" s="25" t="n"/>
-      <c r="F31" s="25" t="n"/>
-      <c r="G31" s="25" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H31" s="25" t="n"/>
-      <c r="I31" s="25" t="n"/>
-      <c r="J31" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0008</t>
-        </is>
-      </c>
-      <c r="K31" s="24" t="inlineStr">
-        <is>
-          <t>Dust/Particulate Control</t>
-        </is>
-      </c>
-      <c r="L31" s="24" t="inlineStr">
-        <is>
-          <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
-        </is>
-      </c>
-      <c r="M31" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N31" s="24" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O31" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E32" s="25" t="n"/>
-      <c r="F32" s="25" t="n"/>
-      <c r="G32" s="25" t="inlineStr">
-        <is>
-          <t>Project-BRS-0004</t>
-        </is>
-      </c>
-      <c r="H32" s="25" t="n"/>
-      <c r="I32" s="25" t="n"/>
-      <c r="J32" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0016</t>
-        </is>
-      </c>
-      <c r="K32" s="24" t="inlineStr">
-        <is>
-          <t>Wastewater Management</t>
-        </is>
-      </c>
-      <c r="L32" s="24" t="inlineStr">
-        <is>
-          <t>The facility must treat and/or contain process wastewater to meet the discharge acceptance criteria at the defined discharge point.</t>
-        </is>
-      </c>
-      <c r="M32" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N32" s="24" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O32" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="25" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="n"/>
-      <c r="F33" s="25" t="n"/>
-      <c r="G33" s="22" t="inlineStr">
-        <is>
-          <t>Project-BRS-0008</t>
-        </is>
-      </c>
-      <c r="H33" s="22" t="inlineStr">
-        <is>
-          <t>Workforce Productivity &amp; Support</t>
-        </is>
-      </c>
-      <c r="I33" s="22" t="inlineStr">
-        <is>
-          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
-        </is>
-      </c>
-      <c r="J33" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0018</t>
-        </is>
-      </c>
-      <c r="K33" s="24" t="inlineStr">
-        <is>
-          <t>Physical Security Zones</t>
-        </is>
-      </c>
-      <c r="L33" s="24" t="inlineStr">
-        <is>
-          <t>The facility must implement access control to restrict entry to production and warehouse areas to authorised personnel only.</t>
-        </is>
-      </c>
-      <c r="M33" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N33" s="24" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O33" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="25" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="n"/>
-      <c r="F34" s="25" t="n"/>
-      <c r="G34" s="25" t="inlineStr">
-        <is>
-          <t>Project-BRS-0008</t>
-        </is>
-      </c>
-      <c r="H34" s="25" t="n"/>
-      <c r="I34" s="25" t="n"/>
-      <c r="J34" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0008</t>
-        </is>
-      </c>
-      <c r="K34" s="24" t="inlineStr">
-        <is>
-          <t>Dust/Particulate Control</t>
-        </is>
-      </c>
-      <c r="L34" s="24" t="inlineStr">
-        <is>
-          <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
-        </is>
-      </c>
-      <c r="M34" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N34" s="24" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O34" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="25" t="n"/>
-      <c r="E35" s="25" t="n"/>
-      <c r="F35" s="25" t="n"/>
-      <c r="G35" s="25" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H35" s="25" t="n"/>
-      <c r="I35" s="25" t="n"/>
-      <c r="J35" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0003</t>
-        </is>
-      </c>
-      <c r="K35" s="24" t="inlineStr">
-        <is>
-          <t>Floor Load Rating</t>
-        </is>
-      </c>
-      <c r="L35" s="24" t="inlineStr">
-        <is>
-          <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
-        </is>
-      </c>
-      <c r="M35" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N35" s="24" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O35" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="25" t="n"/>
-      <c r="E36" s="25" t="n"/>
-      <c r="F36" s="25" t="n"/>
-      <c r="G36" s="25" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="n"/>
-      <c r="I36" s="25" t="n"/>
-      <c r="J36" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0007</t>
-        </is>
-      </c>
-      <c r="K36" s="24" t="inlineStr">
-        <is>
-          <t>Humidity Control</t>
-        </is>
-      </c>
-      <c r="L36" s="24" t="inlineStr">
-        <is>
-          <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
-        </is>
-      </c>
-      <c r="M36" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N36" s="24" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O36" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="25" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="n"/>
-      <c r="F37" s="25" t="n"/>
-      <c r="G37" s="25" t="inlineStr">
-        <is>
-          <t>Project-BRS-0008</t>
-        </is>
-      </c>
-      <c r="H37" s="25" t="n"/>
-      <c r="I37" s="25" t="n"/>
-      <c r="J37" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0001</t>
-        </is>
-      </c>
-      <c r="K37" s="24" t="inlineStr">
-        <is>
-          <t>Site Access &amp; Logistics</t>
-        </is>
-      </c>
-      <c r="L37" s="24" t="inlineStr">
-        <is>
-          <t>The facility must provide segregated heavy-vehicle and light-vehicle access routes from the site boundary to designated loading and parking areas.</t>
-        </is>
-      </c>
-      <c r="M37" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N37" s="24" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O37" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>Safe, Compliant and Sustainable Operations</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="n"/>
+      <c r="H37" s="23" t="n"/>
+      <c r="I37" s="23" t="n"/>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="25" t="n"/>
+      <c r="L37" s="25" t="n"/>
+      <c r="M37" s="25" t="n"/>
+      <c r="N37" s="25" t="n"/>
+      <c r="O37" s="25" t="n"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
       <c r="B38" s="13" t="n"/>
       <c r="C38" s="13" t="n"/>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="27" t="n"/>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="27" t="n"/>
+      <c r="G38" s="27" t="inlineStr">
+        <is>
+          <t>Project-BRS-0002</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="n"/>
+      <c r="I38" s="27" t="n"/>
+      <c r="J38" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0008</t>
+        </is>
+      </c>
+      <c r="K38" s="25" t="inlineStr">
+        <is>
+          <t>Dust/Particulate Control</t>
+        </is>
+      </c>
+      <c r="L38" s="25" t="inlineStr">
+        <is>
+          <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
+        </is>
+      </c>
+      <c r="M38" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N38" s="25" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O38" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18.75" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="13" t="n"/>
+      <c r="D39" s="27" t="n"/>
+      <c r="E39" s="27" t="n"/>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="inlineStr">
+        <is>
+          <t>Project-BRS-0002</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="n"/>
+      <c r="I39" s="27" t="n"/>
+      <c r="J39" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0002</t>
+        </is>
+      </c>
+      <c r="K39" s="25" t="inlineStr">
+        <is>
+          <t>Loading Dock Capacity</t>
+        </is>
+      </c>
+      <c r="L39" s="25" t="inlineStr">
+        <is>
+          <t>The facility must provide loading docks capable of simultaneously servicing the forecast peak number of heavy vehicles defined in the logistics plan.</t>
+        </is>
+      </c>
+      <c r="M39" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N39" s="25" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O39" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18.75" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="13" t="n"/>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="23" t="n"/>
+      <c r="F40" s="23" t="n"/>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>Project-BRS-0002</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>Reliable Manufacturing Capability</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
+        </is>
+      </c>
+      <c r="J40" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0010</t>
+        </is>
+      </c>
+      <c r="K40" s="25" t="inlineStr">
+        <is>
+          <t>Electrical Power Quality</t>
+        </is>
+      </c>
+      <c r="L40" s="25" t="inlineStr">
+        <is>
+          <t>The facility must provide electrical power to production equipment within the specified voltage variation and harmonic distortion limits.</t>
+        </is>
+      </c>
+      <c r="M40" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N40" s="25" t="inlineStr">
+        <is>
+          <t>Technical Requirements</t>
+        </is>
+      </c>
+      <c r="O40" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18.75" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n"/>
+      <c r="C41" s="13" t="n"/>
+      <c r="D41" s="27" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F38" s="22" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="22" t="n"/>
-      <c r="I38" s="22" t="n"/>
-      <c r="J38" s="24" t="n"/>
-      <c r="K38" s="24" t="n"/>
-      <c r="L38" s="24" t="n"/>
-      <c r="M38" s="24" t="n"/>
-      <c r="N38" s="24" t="n"/>
-      <c r="O38" s="24" t="n"/>
-    </row>
-    <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" s="18" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="25" t="n"/>
-      <c r="E39" s="25" t="n"/>
-      <c r="F39" s="25" t="n"/>
-      <c r="G39" s="25" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H39" s="25" t="n"/>
-      <c r="I39" s="25" t="n"/>
-      <c r="J39" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0002</t>
-        </is>
-      </c>
-      <c r="K39" s="24" t="inlineStr">
-        <is>
-          <t>Loading Dock Capacity</t>
-        </is>
-      </c>
-      <c r="L39" s="24" t="inlineStr">
-        <is>
-          <t>The facility must provide loading docks capable of simultaneously servicing the forecast peak number of heavy vehicles defined in the logistics plan.</t>
-        </is>
-      </c>
-      <c r="M39" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N39" s="24" t="inlineStr">
+      <c r="E41" s="27" t="n"/>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="23" t="inlineStr">
+        <is>
+          <t>Project-BRS-0004</t>
+        </is>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Community Stewardship</t>
+        </is>
+      </c>
+      <c r="I41" s="23" t="inlineStr">
+        <is>
+          <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0017</t>
+        </is>
+      </c>
+      <c r="K41" s="25" t="inlineStr">
+        <is>
+          <t>Noise at Boundary</t>
+        </is>
+      </c>
+      <c r="L41" s="25" t="inlineStr">
+        <is>
+          <t>The facility must limit operational noise at the site boundary to not exceed the specified maximum levels.</t>
+        </is>
+      </c>
+      <c r="M41" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N41" s="25" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O39" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="25" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E40" s="25" t="n"/>
-      <c r="F40" s="25" t="n"/>
-      <c r="G40" s="22" t="inlineStr">
-        <is>
-          <t>Project-BRS-0004</t>
-        </is>
-      </c>
-      <c r="H40" s="22" t="inlineStr">
-        <is>
-          <t>Environmental &amp; Community Stewardship</t>
-        </is>
-      </c>
-      <c r="I40" s="22" t="inlineStr">
-        <is>
-          <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
-        </is>
-      </c>
-      <c r="J40" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0017</t>
-        </is>
-      </c>
-      <c r="K40" s="24" t="inlineStr">
-        <is>
-          <t>Noise at Boundary</t>
-        </is>
-      </c>
-      <c r="L40" s="24" t="inlineStr">
-        <is>
-          <t>The facility must limit operational noise at the site boundary to not exceed the specified maximum levels.</t>
-        </is>
-      </c>
-      <c r="M40" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N40" s="24" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O40" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="25" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="n"/>
-      <c r="F41" s="25" t="n"/>
-      <c r="G41" s="26" t="inlineStr">
-        <is>
-          <t>Project-BRS-0004</t>
-        </is>
-      </c>
-      <c r="H41" s="26" t="n"/>
-      <c r="I41" s="26" t="n"/>
-      <c r="J41" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0003</t>
-        </is>
-      </c>
-      <c r="K41" s="24" t="inlineStr">
-        <is>
-          <t>Floor Load Rating</t>
-        </is>
-      </c>
-      <c r="L41" s="24" t="inlineStr">
-        <is>
-          <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
-        </is>
-      </c>
-      <c r="M41" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N41" s="24" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O41" s="24" t="inlineStr">
+      <c r="O41" s="25" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
       <c r="B42" s="11" t="n"/>
       <c r="C42" s="11" t="n"/>
-      <c r="D42" s="25" t="n"/>
-      <c r="E42" s="25" t="n"/>
-      <c r="F42" s="25" t="n"/>
-      <c r="G42" s="26" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
+      <c r="D42" s="26" t="n"/>
+      <c r="E42" s="26" t="n"/>
+      <c r="F42" s="26" t="n"/>
+      <c r="G42" s="26" t="n"/>
       <c r="H42" s="26" t="n"/>
       <c r="I42" s="26" t="n"/>
-      <c r="J42" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0006</t>
-        </is>
-      </c>
-      <c r="K42" s="24" t="inlineStr">
-        <is>
-          <t>Temperature Control</t>
-        </is>
-      </c>
-      <c r="L42" s="24" t="inlineStr">
-        <is>
-          <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
-        </is>
-      </c>
-      <c r="M42" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N42" s="24" t="inlineStr">
+      <c r="J42" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0003</t>
+        </is>
+      </c>
+      <c r="K42" s="25" t="inlineStr">
+        <is>
+          <t>Floor Load Rating</t>
+        </is>
+      </c>
+      <c r="L42" s="25" t="inlineStr">
+        <is>
+          <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
+        </is>
+      </c>
+      <c r="M42" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N42" s="25" t="inlineStr">
+        <is>
+          <t>Technical Requirements</t>
+        </is>
+      </c>
+      <c r="O42" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18.75" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="13" t="n"/>
+      <c r="D43" s="27" t="inlineStr">
+        <is>
+          <t>Project-OBJ-01</t>
+        </is>
+      </c>
+      <c r="E43" s="27" t="n"/>
+      <c r="F43" s="27" t="n"/>
+      <c r="G43" s="27" t="inlineStr">
+        <is>
+          <t>Project-BRS-0008</t>
+        </is>
+      </c>
+      <c r="H43" s="27" t="n"/>
+      <c r="I43" s="27" t="n"/>
+      <c r="J43" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0001</t>
+        </is>
+      </c>
+      <c r="K43" s="25" t="inlineStr">
+        <is>
+          <t>Site Access &amp; Logistics</t>
+        </is>
+      </c>
+      <c r="L43" s="25" t="inlineStr">
+        <is>
+          <t>The facility must provide segregated heavy-vehicle and light-vehicle access routes from the site boundary to designated loading and parking areas.</t>
+        </is>
+      </c>
+      <c r="M43" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N43" s="25" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O42" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="O43" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18.75" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="25" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="n"/>
-      <c r="F43" s="25" t="n"/>
-      <c r="G43" s="25" t="inlineStr">
-        <is>
-          <t>Project-BRS-0008</t>
-        </is>
-      </c>
-      <c r="H43" s="25" t="n"/>
-      <c r="I43" s="25" t="n"/>
-      <c r="J43" s="24" t="inlineStr">
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="13" t="n"/>
+      <c r="D44" s="27" t="n"/>
+      <c r="E44" s="27" t="n"/>
+      <c r="F44" s="27" t="n"/>
+      <c r="G44" s="27" t="inlineStr">
+        <is>
+          <t>Project-BRS-0002</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="n"/>
+      <c r="I44" s="27" t="n"/>
+      <c r="J44" s="25" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
         </is>
       </c>
-      <c r="K43" s="24" t="inlineStr">
+      <c r="K44" s="25" t="inlineStr">
         <is>
           <t>Humidity Control</t>
         </is>
       </c>
-      <c r="L43" s="24" t="inlineStr">
+      <c r="L44" s="25" t="inlineStr">
         <is>
           <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
         </is>
       </c>
-      <c r="M43" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N43" s="24" t="inlineStr">
+      <c r="M44" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N44" s="25" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O43" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18.75" customHeight="1">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="O44" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18.75" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="25" t="n"/>
-      <c r="E44" s="25" t="n"/>
-      <c r="F44" s="25" t="n"/>
-      <c r="G44" s="22" t="n"/>
-      <c r="H44" s="22" t="n"/>
-      <c r="I44" s="22" t="n"/>
-      <c r="J44" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0005</t>
-        </is>
-      </c>
-      <c r="K44" s="24" t="inlineStr">
-        <is>
-          <t>Building Envelope Tightness</t>
-        </is>
-      </c>
-      <c r="L44" s="24" t="inlineStr">
-        <is>
-          <t>The building envelope must achieve air leakage performance not exceeding the nominated threshold.</t>
-        </is>
-      </c>
-      <c r="M44" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N44" s="24" t="inlineStr">
+      <c r="B45" s="13" t="n"/>
+      <c r="C45" s="13" t="n"/>
+      <c r="D45" s="27" t="n"/>
+      <c r="E45" s="27" t="n"/>
+      <c r="F45" s="27" t="n"/>
+      <c r="G45" s="27" t="inlineStr">
+        <is>
+          <t>Project-BRS-0002</t>
+        </is>
+      </c>
+      <c r="H45" s="27" t="n"/>
+      <c r="I45" s="27" t="n"/>
+      <c r="J45" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0009</t>
+        </is>
+      </c>
+      <c r="K45" s="25" t="inlineStr">
+        <is>
+          <t>Compressed Air Quality</t>
+        </is>
+      </c>
+      <c r="L45" s="25" t="inlineStr">
+        <is>
+          <t>The facility must supply compressed air to production equipment at the specified pressure, flow, and cleanliness class at each point of use.</t>
+        </is>
+      </c>
+      <c r="M45" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N45" s="25" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O44" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18.75" customHeight="1">
-      <c r="A45" s="18" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="22" t="n"/>
-      <c r="F45" s="22" t="n"/>
-      <c r="G45" s="22" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H45" s="22" t="inlineStr">
-        <is>
-          <t>Reliable Manufacturing Capability</t>
-        </is>
-      </c>
-      <c r="I45" s="22" t="inlineStr">
-        <is>
-          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
-        </is>
-      </c>
-      <c r="J45" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0010</t>
-        </is>
-      </c>
-      <c r="K45" s="24" t="inlineStr">
-        <is>
-          <t>Electrical Power Quality</t>
-        </is>
-      </c>
-      <c r="L45" s="24" t="inlineStr">
-        <is>
-          <t>The facility must provide electrical power to production equipment within the specified voltage variation and harmonic distortion limits.</t>
-        </is>
-      </c>
-      <c r="M45" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N45" s="24" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O45" s="24" t="inlineStr">
+      <c r="O45" s="25" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3007,57 +3048,57 @@
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="n"/>
-      <c r="J46" s="17" t="inlineStr">
+      <c r="J46" s="18" t="inlineStr">
         <is>
           <t>Project-SRS-0004</t>
         </is>
       </c>
-      <c r="K46" s="17" t="inlineStr">
+      <c r="K46" s="18" t="inlineStr">
         <is>
           <t>Floor Flatness</t>
         </is>
       </c>
-      <c r="L46" s="17" t="inlineStr">
+      <c r="L46" s="18" t="inlineStr">
         <is>
           <t>The production floor must achieve the specified flatness and levelness tolerances required by precision manufacturing equipment.</t>
         </is>
       </c>
-      <c r="M46" s="17" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N46" s="17" t="inlineStr">
+      <c r="M46" s="18" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N46" s="18" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O46" s="17" t="inlineStr">
+      <c r="O46" s="18" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000113</t>
         </is>
       </c>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
-      <c r="F47" s="17" t="n"/>
-      <c r="G47" s="17" t="n"/>
-      <c r="H47" s="17" t="n"/>
-      <c r="I47" s="17" t="n"/>
-      <c r="J47" s="17" t="n"/>
-      <c r="K47" s="17" t="n"/>
-      <c r="L47" s="17" t="n"/>
-      <c r="M47" s="17" t="n"/>
-      <c r="N47" s="17" t="n"/>
-      <c r="O47" s="17" t="n"/>
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="18" t="n"/>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="18" t="n"/>
+      <c r="H47" s="18" t="n"/>
+      <c r="I47" s="18" t="n"/>
+      <c r="J47" s="18" t="n"/>
+      <c r="K47" s="18" t="n"/>
+      <c r="L47" s="18" t="n"/>
+      <c r="M47" s="18" t="n"/>
+      <c r="N47" s="18" t="n"/>
+      <c r="O47" s="18" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -3073,62 +3114,58 @@
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="n"/>
-      <c r="J48" s="17" t="inlineStr">
+      <c r="J48" s="18" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
         </is>
       </c>
-      <c r="K48" s="17" t="n"/>
-      <c r="L48" s="17" t="n"/>
-      <c r="M48" s="17" t="n"/>
-      <c r="N48" s="17" t="n"/>
-      <c r="O48" s="17" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000121</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="27" t="n"/>
-      <c r="E49" s="27" t="n"/>
-      <c r="F49" s="27" t="n"/>
-      <c r="G49" s="27" t="n"/>
-      <c r="H49" s="27" t="n"/>
-      <c r="I49" s="27" t="n"/>
-      <c r="J49" s="24" t="inlineStr">
-        <is>
-          <t>Project-SRS-0020</t>
-        </is>
-      </c>
-      <c r="K49" s="27" t="n"/>
-      <c r="L49" s="27" t="n"/>
-      <c r="M49" s="27" t="n"/>
-      <c r="N49" s="27" t="n"/>
-      <c r="O49" s="27" t="n"/>
-    </row>
-    <row r="50" ht="18.75" customHeight="1">
-      <c r="A50" s="24" t="inlineStr">
+      <c r="K48" s="18" t="n"/>
+      <c r="L48" s="18" t="n"/>
+      <c r="M48" s="18" t="n"/>
+      <c r="N48" s="18" t="n"/>
+      <c r="O48" s="18" t="n"/>
+    </row>
+    <row r="49" ht="18.75" customHeight="1">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000112</t>
         </is>
       </c>
-      <c r="B50" s="24" t="n"/>
-      <c r="C50" s="24" t="n"/>
-      <c r="D50" s="24" t="n"/>
-      <c r="E50" s="24" t="n"/>
-      <c r="F50" s="24" t="n"/>
-      <c r="G50" s="24" t="n"/>
-      <c r="H50" s="24" t="n"/>
-      <c r="I50" s="24" t="n"/>
-      <c r="J50" s="24" t="n"/>
-      <c r="K50" s="24" t="n"/>
-      <c r="L50" s="24" t="n"/>
-      <c r="M50" s="24" t="n"/>
-      <c r="N50" s="24" t="n"/>
-      <c r="O50" s="24" t="n"/>
+      <c r="B49" s="25" t="n"/>
+      <c r="C49" s="25" t="n"/>
+      <c r="D49" s="25" t="n"/>
+      <c r="E49" s="25" t="n"/>
+      <c r="F49" s="25" t="n"/>
+      <c r="G49" s="25" t="n"/>
+      <c r="H49" s="25" t="n"/>
+      <c r="I49" s="25" t="n"/>
+      <c r="J49" s="25" t="n"/>
+      <c r="K49" s="25" t="n"/>
+      <c r="L49" s="25" t="n"/>
+      <c r="M49" s="25" t="n"/>
+      <c r="N49" s="25" t="n"/>
+      <c r="O49" s="25" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="28" t="inlineStr">
+        <is>
+          <t>Project- PSTR-99999</t>
+        </is>
+      </c>
+      <c r="B50" s="29" t="n"/>
+      <c r="C50" s="29" t="n"/>
+      <c r="D50" s="28" t="n"/>
+      <c r="E50" s="29" t="n"/>
+      <c r="F50" s="29" t="n"/>
+      <c r="G50" s="28" t="n"/>
+      <c r="H50" s="30" t="n"/>
+      <c r="I50" s="30" t="n"/>
+      <c r="J50" s="28" t="n"/>
+      <c r="K50" s="29" t="n"/>
+      <c r="L50" s="29" t="n"/>
+      <c r="M50" s="29" t="n"/>
+      <c r="N50" s="29" t="n"/>
+      <c r="O50" s="29" t="n"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -3138,45 +3175,70 @@
       </c>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="5" t="n"/>
-      <c r="D51" s="24" t="n"/>
-      <c r="E51" s="24" t="n"/>
-      <c r="F51" s="24" t="n"/>
-      <c r="G51" s="24" t="n"/>
-      <c r="H51" s="24" t="n"/>
-      <c r="I51" s="24" t="n"/>
-      <c r="J51" s="24" t="inlineStr">
+      <c r="D51" s="25" t="n"/>
+      <c r="E51" s="25" t="n"/>
+      <c r="F51" s="25" t="n"/>
+      <c r="G51" s="25" t="n"/>
+      <c r="H51" s="25" t="n"/>
+      <c r="I51" s="25" t="n"/>
+      <c r="J51" s="25" t="inlineStr">
         <is>
           <t>Project-SRS-0004</t>
         </is>
       </c>
-      <c r="K51" s="24" t="inlineStr">
+      <c r="K51" s="25" t="inlineStr">
         <is>
           <t>Floor Flatness</t>
         </is>
       </c>
-      <c r="L51" s="24" t="inlineStr">
+      <c r="L51" s="25" t="inlineStr">
         <is>
           <t>The production floor must achieve the specified flatness and levelness tolerances required by precision manufacturing equipment.</t>
         </is>
       </c>
-      <c r="M51" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N51" s="24" t="inlineStr">
+      <c r="M51" s="25" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N51" s="25" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O51" s="24" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
+      <c r="O51" s="25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000121</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="31" t="n"/>
+      <c r="E52" s="31" t="n"/>
+      <c r="F52" s="31" t="n"/>
+      <c r="G52" s="31" t="n"/>
+      <c r="H52" s="31" t="n"/>
+      <c r="I52" s="31" t="n"/>
+      <c r="J52" s="25" t="inlineStr">
+        <is>
+          <t>Project-SRS-0020</t>
+        </is>
+      </c>
+      <c r="K52" s="31" t="n"/>
+      <c r="L52" s="31" t="n"/>
+      <c r="M52" s="31" t="n"/>
+      <c r="N52" s="31" t="n"/>
+      <c r="O52" s="31" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O51"/>
+  <autoFilter ref="A1:O52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3188,9 +3250,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.54296875" bestFit="1" customWidth="1" style="6" min="1" max="15"/>
+    <col width="30.5703125" bestFit="1" customWidth="1" style="6" min="1" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="33" customFormat="1" customHeight="1" s="1">
@@ -3276,18 +3338,18 @@
           <t>Project-PS&amp;TR-B-000100</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n"/>
-      <c r="C2" s="13" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
       <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Project-OBJ-02</t>
         </is>
       </c>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
       <c r="G2" s="10" t="n"/>
-      <c r="H2" s="13" t="n"/>
-      <c r="I2" s="13" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
       <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
@@ -3320,15 +3382,15 @@
       </c>
     </row>
     <row r="3" ht="70.5" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="12" t="n"/>
-      <c r="B3" s="12" t="n"/>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="12" t="n"/>
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="11" t="n"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0009</t>
@@ -3366,19 +3428,19 @@
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="n"/>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="12" t="n"/>
       <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Safe, Compliant and Sustainable Operations</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
@@ -3388,12 +3450,12 @@
           <t>Project-BRS-0001</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>Safe, Efficient &amp; Compliant Operations</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall enable safe, efficient, and legally compliant manufacturing operations across all production, logistics, and support activities to protect personnel, assets, and regulatory approvals.</t>
         </is>
@@ -3430,15 +3492,15 @@
       </c>
     </row>
     <row r="5" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0014</t>
@@ -3471,15 +3533,15 @@
       </c>
     </row>
     <row r="6" ht="70.5" customFormat="1" customHeight="1" s="1">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="12" t="n"/>
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
       <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0001</t>
@@ -3512,23 +3574,23 @@
       </c>
     </row>
     <row r="7" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
       <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>Workforce Productivity &amp; Support</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
         </is>
@@ -3565,15 +3627,15 @@
       </c>
     </row>
     <row r="8" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="13" t="n"/>
       <c r="J8" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
@@ -3606,15 +3668,15 @@
       </c>
     </row>
     <row r="9" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="13" t="n"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
@@ -3647,15 +3709,15 @@
       </c>
     </row>
     <row r="10" ht="70.5" customFormat="1" customHeight="1" s="1">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="n"/>
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="13" t="n"/>
       <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0001</t>
@@ -3688,15 +3750,15 @@
       </c>
     </row>
     <row r="11" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
@@ -3729,23 +3791,23 @@
       </c>
     </row>
     <row r="12" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Project-BRS-0004</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>Environmental &amp; Community Stewardship</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
         </is>
@@ -3782,15 +3844,15 @@
       </c>
     </row>
     <row r="13" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0016</t>
@@ -3823,15 +3885,15 @@
       </c>
     </row>
     <row r="14" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
       <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -3864,12 +3926,12 @@
       </c>
     </row>
     <row r="15" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
@@ -3905,23 +3967,23 @@
       </c>
     </row>
     <row r="16" ht="70.5" customFormat="1" customHeight="1" s="1">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
       <c r="D16" s="10" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
       <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Project-BRS-0002</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>Reliable Manufacturing Capability</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
         </is>
@@ -3958,15 +4020,15 @@
       </c>
     </row>
     <row r="17" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="n"/>
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="13" t="n"/>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
@@ -3999,15 +4061,15 @@
       </c>
     </row>
     <row r="18" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="11" t="n"/>
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="13" t="n"/>
       <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
@@ -4040,15 +4102,15 @@
       </c>
     </row>
     <row r="19" ht="70.5" customFormat="1" customHeight="1" s="1">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="n"/>
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
       <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0002</t>
@@ -4081,15 +4143,15 @@
       </c>
     </row>
     <row r="20" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
-      <c r="I20" s="11" t="n"/>
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="13" t="n"/>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -4122,15 +4184,15 @@
       </c>
     </row>
     <row r="21" ht="70.5" customFormat="1" customHeight="1" s="1">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="13" t="n"/>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0009</t>
@@ -4163,15 +4225,15 @@
       </c>
     </row>
     <row r="22" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
       <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
@@ -4204,15 +4266,15 @@
       </c>
     </row>
     <row r="23" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
       <c r="G23" s="10" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0005</t>
@@ -4245,15 +4307,15 @@
       </c>
     </row>
     <row r="24" ht="57.75" customFormat="1" customHeight="1" s="1">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="11" t="n"/>
       <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -4483,10 +4545,10 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="G16:G22"/>
     <mergeCell ref="F4:F15"/>
+    <mergeCell ref="E16:E24"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="E16:E24"/>
+    <mergeCell ref="H4:H6"/>
     <mergeCell ref="G12:G14"/>
-    <mergeCell ref="H4:H6"/>
     <mergeCell ref="E4:E15"/>
     <mergeCell ref="I23:I24"/>
     <mergeCell ref="G7:G11"/>
@@ -4500,6 +4562,14 @@
     <mergeCell ref="I2:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Aptos"&amp;10 &amp;K000000_x000d_# Mott MacDonald Restricted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4509,10 +4579,10 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:O49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.54296875" bestFit="1" customWidth="1" style="6" min="1" max="15"/>
+    <col width="30.5703125" bestFit="1" customWidth="1" style="6" min="1" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
@@ -4592,49 +4662,53 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Project- PSTR-99999</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="16" t="n"/>
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n"/>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Safe, Compliant and Sustainable Operations</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="14" t="n"/>
-      <c r="I2" s="14" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-    </row>
-    <row r="3" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="11" t="n"/>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="5" t="n"/>
       <c r="L3" s="5" t="n"/>
@@ -4643,15 +4717,15 @@
       <c r="O3" s="5" t="n"/>
     </row>
     <row r="4" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A4" s="11" t="n"/>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="15" t="n"/>
-      <c r="I4" s="15" t="n"/>
+      <c r="A4" s="13" t="n"/>
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="13" t="n"/>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="5" t="n"/>
       <c r="L4" s="5" t="n"/>
@@ -4660,708 +4734,684 @@
       <c r="O4" s="5" t="n"/>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>Workforce Productivity &amp; Support</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0018</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Physical Security Zones</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>The facility must implement access control to restrict entry to production and warehouse areas to authorised personnel only.</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Dust/Particulate Control</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="13" t="n"/>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>Humidity Control</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0001</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Site Access &amp; Logistics</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>The facility must provide segregated heavy-vehicle and light-vehicle access routes from the site boundary to designated loading and parking areas.</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Temperature Control</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Project-BRS-0004</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>Environmental &amp; Community Stewardship</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0017</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Noise at Boundary</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>The facility must limit operational noise at the site boundary to not exceed the specified maximum levels.</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="13" t="n"/>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0016</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>Wastewater Management</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>The facility must treat and/or contain process wastewater to meet the discharge acceptance criteria at the defined discharge point.</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>Floor Load Rating</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Project-BRS-0002</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>Reliable Manufacturing Capability</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0010</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Electrical Power Quality</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>The facility must provide electrical power to production equipment within the specified voltage variation and harmonic distortion limits.</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="13" t="n"/>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>Dust/Particulate Control</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
-      <c r="I16" s="11" t="n"/>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="13" t="n"/>
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>Humidity Control</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="13" t="n"/>
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0002</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>Loading Dock Capacity</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>The facility must provide loading docks capable of simultaneously servicing the forecast peak number of heavy vehicles defined in the logistics plan.</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="11" t="n"/>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Floor Load Rating</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="13" t="n"/>
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0009</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Compressed Air Quality</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>The facility must supply compressed air to production equipment at the specified pressure, flow, and cleanliness class at each point of use.</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Temperature Control</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Project-SRS-0005</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Building Envelope Tightness</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>The building envelope must achieve air leakage performance not exceeding the nominated threshold.</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t>Draft</t>
@@ -5369,89 +5419,113 @@
       </c>
     </row>
     <row r="22" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="10" t="n"/>
       <c r="H22" s="12" t="n"/>
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="4" t="inlineStr">
         <is>
+          <t>Project-SRS-0005</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Building Envelope Tightness</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>The building envelope must achieve air leakage performance not exceeding the nominated threshold.</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>Technical Requirements</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
           <t>Project-SRS-0003</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>Floor Load Rating</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Safe, Compliant and Sustainable Operations</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="n"/>
-      <c r="I24" s="11" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="5" t="n"/>
       <c r="L24" s="5" t="n"/>
@@ -5460,15 +5534,15 @@
       <c r="O24" s="5" t="n"/>
     </row>
     <row r="25" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="5" t="n"/>
       <c r="L25" s="5" t="n"/>
@@ -5477,732 +5551,708 @@
       <c r="O25" s="5" t="n"/>
     </row>
     <row r="26" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="11" t="n"/>
+      <c r="I26" s="11" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>Workforce Productivity &amp; Support</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0018</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>Physical Security Zones</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>The facility must implement access control to restrict entry to production and warehouse areas to authorised personnel only.</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="11" t="n"/>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="13" t="n"/>
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>Dust/Particulate Control</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="11" t="n"/>
-      <c r="I28" s="11" t="n"/>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="13" t="n"/>
+      <c r="I29" s="13" t="n"/>
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>Humidity Control</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="13" t="n"/>
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0001</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Site Access &amp; Logistics</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>The facility must provide segregated heavy-vehicle and light-vehicle access routes from the site boundary to designated loading and parking areas.</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>Temperature Control</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Project-BRS-0004</t>
         </is>
       </c>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>Environmental &amp; Community Stewardship</t>
         </is>
       </c>
-      <c r="I31" s="13" t="inlineStr">
+      <c r="I32" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0017</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Noise at Boundary</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>The facility must limit operational noise at the site boundary to not exceed the specified maximum levels.</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="11" t="n"/>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="13" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="13" t="n"/>
+      <c r="H33" s="13" t="n"/>
+      <c r="I33" s="13" t="n"/>
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0016</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>Wastewater Management</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>The facility must treat and/or contain process wastewater to meet the discharge acceptance criteria at the defined discharge point.</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="12" t="n"/>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="12" t="n"/>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="13" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="11" t="n"/>
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>Floor Load Rating</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>Floor Load Rating</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>Project-BRS-0002</t>
         </is>
       </c>
-      <c r="H35" s="13" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>Reliable Manufacturing Capability</t>
         </is>
       </c>
-      <c r="I35" s="13" t="inlineStr">
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0010</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Electrical Power Quality</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>The facility must provide electrical power to production equipment within the specified voltage variation and harmonic distortion limits.</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="11" t="n"/>
-      <c r="I36" s="11" t="n"/>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="13" t="n"/>
+      <c r="H37" s="13" t="n"/>
+      <c r="I37" s="13" t="n"/>
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>Dust/Particulate Control</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="13" t="n"/>
+      <c r="H38" s="13" t="n"/>
+      <c r="I38" s="13" t="n"/>
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>Humidity Control</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A38" s="11" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="11" t="n"/>
-      <c r="I38" s="11" t="n"/>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="13" t="n"/>
+      <c r="D39" s="13" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="13" t="n"/>
+      <c r="H39" s="13" t="n"/>
+      <c r="I39" s="13" t="n"/>
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0002</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>Loading Dock Capacity</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>The facility must provide loading docks capable of simultaneously servicing the forecast peak number of heavy vehicles defined in the logistics plan.</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
-      <c r="H39" s="11" t="n"/>
-      <c r="I39" s="11" t="n"/>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="13" t="n"/>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="13" t="n"/>
+      <c r="H40" s="13" t="n"/>
+      <c r="I40" s="13" t="n"/>
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>Floor Load Rating</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A40" s="11" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="11" t="n"/>
-      <c r="H40" s="11" t="n"/>
-      <c r="I40" s="11" t="n"/>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="13" t="n"/>
+      <c r="C41" s="13" t="n"/>
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="13" t="n"/>
+      <c r="I41" s="13" t="n"/>
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0009</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>Compressed Air Quality</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>The facility must supply compressed air to production equipment at the specified pressure, flow, and cleanliness class at each point of use.</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n"/>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="13" t="n"/>
+      <c r="C42" s="13" t="n"/>
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="11" t="n"/>
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>Temperature Control</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A42" s="11" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="10" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="13" t="n"/>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Project-SRS-0005</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>Building Envelope Tightness</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>The building envelope must achieve air leakage performance not exceeding the nominated threshold.</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
           <t>Draft</t>
@@ -6210,73 +6260,69 @@
       </c>
     </row>
     <row r="43" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A43" s="12" t="n"/>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="13" t="n"/>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="10" t="n"/>
       <c r="H43" s="12" t="n"/>
       <c r="I43" s="12" t="n"/>
       <c r="J43" s="4" t="inlineStr">
         <is>
+          <t>Project-SRS-0005</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>Building Envelope Tightness</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>The building envelope must achieve air leakage performance not exceeding the nominated threshold.</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>Technical Requirements</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18.75" customFormat="1" customHeight="1" s="1">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="11" t="n"/>
+      <c r="I44" s="11" t="n"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
           <t>Project-SRS-0003</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>Floor Load Rating</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N43" s="5" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18.75" customFormat="1" customHeight="1" s="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000110</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>Project-SRS-0004</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>Floor Flatness</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>The production floor must achieve the specified flatness and levelness tolerances required by precision manufacturing equipment.</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -6298,7 +6344,7 @@
     <row r="45" ht="18.75" customFormat="1" customHeight="1" s="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Project-PS&amp;TR-B-000111</t>
+          <t>Project-PS&amp;TR-B-000110</t>
         </is>
       </c>
       <c r="B45" s="5" t="n"/>
@@ -6309,17 +6355,41 @@
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="5" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="5" t="n"/>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="n"/>
-      <c r="O45" s="5" t="n"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>Project-SRS-0004</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Floor Flatness</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>The production floor must achieve the specified flatness and levelness tolerances required by precision manufacturing equipment.</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>Technical Requirements</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="18.75" customFormat="1" customHeight="1" s="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Project-PS&amp;TR-B-000112</t>
+          <t>Project-PS&amp;TR-B-000111</t>
         </is>
       </c>
       <c r="B46" s="5" t="n"/>
@@ -6337,10 +6407,10 @@
       <c r="N46" s="5" t="n"/>
       <c r="O46" s="5" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="18.75" customFormat="1" customHeight="1" s="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Project-PS&amp;TR-B-000120</t>
+          <t>Project-PS&amp;TR-B-000112</t>
         </is>
       </c>
       <c r="B47" s="5" t="n"/>
@@ -6359,81 +6429,110 @@
       <c r="O47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000120</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000121</t>
         </is>
       </c>
-      <c r="B48" s="8" t="n"/>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="9" t="n"/>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
-      <c r="G48" s="9" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>Project-SRS-0020</t>
         </is>
       </c>
-      <c r="K48" s="8" t="n"/>
-      <c r="L48" s="8" t="n"/>
-      <c r="M48" s="8" t="n"/>
-      <c r="N48" s="8" t="n"/>
-      <c r="O48" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="E35:E43"/>
-    <mergeCell ref="G5:G9"/>
-    <mergeCell ref="I5:I9"/>
-    <mergeCell ref="C23:C43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="I23:I25"/>
-    <mergeCell ref="F35:F43"/>
-    <mergeCell ref="D23:D34"/>
-    <mergeCell ref="I14:I20"/>
-    <mergeCell ref="G26:G30"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="I31:I33"/>
-    <mergeCell ref="G14:G20"/>
-    <mergeCell ref="I10:I12"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="H23:H25"/>
-    <mergeCell ref="G35:G41"/>
-    <mergeCell ref="B2:B22"/>
-    <mergeCell ref="I35:I41"/>
-    <mergeCell ref="E2:E13"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="D14:D22"/>
-    <mergeCell ref="F14:F22"/>
-    <mergeCell ref="D2:D13"/>
-    <mergeCell ref="B23:B43"/>
-    <mergeCell ref="H26:H30"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="H5:H9"/>
-    <mergeCell ref="H14:H20"/>
-    <mergeCell ref="E23:E34"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="A2:A22"/>
-    <mergeCell ref="H31:H33"/>
-    <mergeCell ref="H35:H41"/>
-    <mergeCell ref="D35:D43"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="E14:E22"/>
-    <mergeCell ref="I26:I30"/>
-    <mergeCell ref="F2:F13"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="C2:C22"/>
-    <mergeCell ref="F23:F34"/>
-    <mergeCell ref="A23:A43"/>
+    <mergeCell ref="G15:G21"/>
+    <mergeCell ref="F36:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="D36:D44"/>
+    <mergeCell ref="H36:H42"/>
+    <mergeCell ref="C3:C23"/>
+    <mergeCell ref="E3:E14"/>
+    <mergeCell ref="E15:E23"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="C24:C44"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="A24:A44"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="H27:H31"/>
+    <mergeCell ref="E36:E44"/>
+    <mergeCell ref="B3:B23"/>
+    <mergeCell ref="D15:D23"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="E24:E35"/>
+    <mergeCell ref="H15:H21"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I15:I21"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="F3:F14"/>
+    <mergeCell ref="A3:A23"/>
+    <mergeCell ref="F24:F35"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="G27:G31"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="G36:G42"/>
+    <mergeCell ref="I27:I31"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="I36:I42"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="D3:D14"/>
+    <mergeCell ref="F15:F23"/>
+    <mergeCell ref="G6:G10"/>
+    <mergeCell ref="B24:B44"/>
+    <mergeCell ref="D24:D35"/>
+    <mergeCell ref="H32:H34"/>
+    <mergeCell ref="I24:I26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Aptos"&amp;10 &amp;K000000_x000d_# Mott MacDonald Restricted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>